--- a/data/trans_orig/P1802_2016_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1802_2016_2023-Clase-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>53581</t>
+          <t>53095</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>86888</t>
+          <t>86317</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>40474</t>
+          <t>40433</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>69027</t>
+          <t>68951</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>101527</t>
+          <t>103571</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>142794</t>
+          <t>143689</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,51%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>342204</t>
+          <t>342775</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>375511</t>
+          <t>375997</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>278028</t>
+          <t>278104</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>306581</t>
+          <t>306622</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>633353</t>
+          <t>632458</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>674620</t>
+          <t>672576</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>86,66%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34571</t>
+          <t>35751</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60491</t>
+          <t>62630</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>49805</t>
+          <t>51164</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>80268</t>
+          <t>80662</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>92952</t>
+          <t>91486</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>133431</t>
+          <t>133242</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,78%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>316736</t>
+          <t>314597</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>342656</t>
+          <t>341476</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>83,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>292005</t>
+          <t>291611</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>322468</t>
+          <t>321109</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>78,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>616069</t>
+          <t>616258</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>656548</t>
+          <t>658014</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,79%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>64422</t>
+          <t>64985</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>98180</t>
+          <t>98219</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29895</t>
+          <t>30179</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52966</t>
+          <t>53625</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>101467</t>
+          <t>102689</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>141420</t>
+          <t>144140</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,95%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>423734</t>
+          <t>423695</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>457492</t>
+          <t>456929</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>113157</t>
+          <t>112498</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>136228</t>
+          <t>135944</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,12%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>81,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>546616</t>
+          <t>543896</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>586569</t>
+          <t>585347</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>79,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,08%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>152697</t>
+          <t>153080</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>202458</t>
+          <t>201431</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>136710</t>
+          <t>138535</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>182947</t>
+          <t>182863</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>303990</t>
+          <t>300629</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>369177</t>
+          <t>369346</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,7%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>947180</t>
+          <t>948207</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>996941</t>
+          <t>996558</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>642929</t>
+          <t>643013</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>689166</t>
+          <t>687341</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>77,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1606337</t>
+          <t>1606168</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1671524</t>
+          <t>1674885</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>84,78%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>72274</t>
+          <t>68973</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>104472</t>
+          <t>104523</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>120518</t>
+          <t>118841</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>161555</t>
+          <t>162836</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>198565</t>
+          <t>196746</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>253928</t>
+          <t>252489</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,58%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>516234</t>
+          <t>516183</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>548432</t>
+          <t>551733</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>576689</t>
+          <t>575408</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>617726</t>
+          <t>619403</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1105022</t>
+          <t>1106461</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1160385</t>
+          <t>1162204</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,52%</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2426,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19042</t>
+          <t>19251</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>39714</t>
+          <t>40358</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>186401</t>
+          <t>188474</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>238388</t>
+          <t>240809</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>213203</t>
+          <t>214440</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>271446</t>
+          <t>274891</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>20,08%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>247431</t>
+          <t>246787</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>268103</t>
+          <t>267894</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>843637</t>
+          <t>841216</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>895624</t>
+          <t>893551</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>77,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1097724</t>
+          <t>1094279</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1155967</t>
+          <t>1154730</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>79,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>84,34%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>449743</t>
+          <t>447292</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>531761</t>
+          <t>532357</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>623933</t>
+          <t>624558</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>724227</t>
+          <t>723218</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1090399</t>
+          <t>1092846</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1220046</t>
+          <t>1220016</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2853961</t>
+          <t>2853365</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2935979</t>
+          <t>2938430</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2807369</t>
+          <t>2808378</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2907663</t>
+          <t>2907038</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>82,32%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5697272</t>
+          <t>5697302</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5826919</t>
+          <t>5824472</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,2%</t>
         </is>
       </c>
     </row>
@@ -3361,32 +3361,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>88948</t>
+          <t>90010</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>73104</t>
+          <t>74077</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>108140</t>
+          <t>109340</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3396,32 +3396,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>99680</t>
+          <t>108995</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>86260</t>
+          <t>94725</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>115528</t>
+          <t>125191</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3431,32 +3431,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>188628</t>
+          <t>199005</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>166138</t>
+          <t>175981</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>211725</t>
+          <t>224729</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>21,66%</t>
         </is>
       </c>
     </row>
@@ -3474,32 +3474,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>415517</t>
+          <t>459734</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>396325</t>
+          <t>440404</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>431361</t>
+          <t>475667</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3509,32 +3509,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>347236</t>
+          <t>378783</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>331388</t>
+          <t>362587</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>360656</t>
+          <t>393053</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3544,32 +3544,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>762754</t>
+          <t>838517</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>739657</t>
+          <t>812793</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>785244</t>
+          <t>861541</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>80,82%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>83,04%</t>
         </is>
       </c>
     </row>
@@ -3587,17 +3587,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>504465</t>
+          <t>549744</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>504465</t>
+          <t>549744</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>504465</t>
+          <t>549744</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3622,17 +3622,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>446916</t>
+          <t>487778</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>446916</t>
+          <t>487778</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>446916</t>
+          <t>487778</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3657,17 +3657,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>951382</t>
+          <t>1037522</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>951382</t>
+          <t>1037522</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>951382</t>
+          <t>1037522</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3704,32 +3704,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>74290</t>
+          <t>73929</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>57773</t>
+          <t>58166</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>93481</t>
+          <t>91061</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3739,32 +3739,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>78286</t>
+          <t>85439</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>66145</t>
+          <t>72112</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>92447</t>
+          <t>100309</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3774,32 +3774,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>152576</t>
+          <t>159368</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>132753</t>
+          <t>139034</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>175494</t>
+          <t>180474</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>19,93%</t>
         </is>
       </c>
     </row>
@@ -3817,32 +3817,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>377923</t>
+          <t>409283</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>358732</t>
+          <t>392151</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>394440</t>
+          <t>425046</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>81,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3852,32 +3852,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>303636</t>
+          <t>337021</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>289475</t>
+          <t>322151</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>315777</t>
+          <t>350348</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>82,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3887,32 +3887,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>681558</t>
+          <t>746304</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>658640</t>
+          <t>725198</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>701381</t>
+          <t>766638</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>82,4%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>84,65%</t>
         </is>
       </c>
     </row>
@@ -3930,17 +3930,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3965,17 +3965,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>381922</t>
+          <t>422460</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>381922</t>
+          <t>422460</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>381922</t>
+          <t>422460</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4000,17 +4000,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834134</t>
+          <t>905672</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834134</t>
+          <t>905672</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834134</t>
+          <t>905672</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4047,32 +4047,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>311858</t>
+          <t>71777</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>98857</t>
+          <t>57986</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>526426</t>
+          <t>89034</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4082,17 +4082,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>35873</t>
+          <t>40291</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28322</t>
+          <t>31504</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45609</t>
+          <t>52023</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4117,32 +4117,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>347731</t>
+          <t>112068</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>138584</t>
+          <t>96854</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>609025</t>
+          <t>132591</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>72,92%</t>
+          <t>20,12%</t>
         </is>
       </c>
     </row>
@@ -4160,32 +4160,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>356406</t>
+          <t>399835</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>141838</t>
+          <t>382578</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>569407</t>
+          <t>413626</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4195,17 +4195,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>131038</t>
+          <t>147206</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>121302</t>
+          <t>135474</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>138589</t>
+          <t>155993</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>72,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4230,32 +4230,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>487444</t>
+          <t>547041</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>226150</t>
+          <t>526518</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>696591</t>
+          <t>562255</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>85,31%</t>
         </is>
       </c>
     </row>
@@ -4273,17 +4273,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4308,17 +4308,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4343,17 +4343,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4390,32 +4390,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>182962</t>
+          <t>194596</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>159164</t>
+          <t>168569</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>209090</t>
+          <t>221209</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4425,32 +4425,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>162739</t>
+          <t>183675</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>80067</t>
+          <t>165644</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>212467</t>
+          <t>206061</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4460,32 +4460,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>345702</t>
+          <t>378271</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>240040</t>
+          <t>345483</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>397671</t>
+          <t>413841</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>20,79%</t>
         </is>
       </c>
     </row>
@@ -4503,32 +4503,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>851144</t>
+          <t>936450</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>825016</t>
+          <t>909837</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>874942</t>
+          <t>962477</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4538,32 +4538,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>814041</t>
+          <t>676217</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>764313</t>
+          <t>653831</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>896713</t>
+          <t>694248</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>76,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4573,32 +4573,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1665185</t>
+          <t>1612667</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1613216</t>
+          <t>1577097</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1770847</t>
+          <t>1645455</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>79,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>82,65%</t>
         </is>
       </c>
     </row>
@@ -4616,17 +4616,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034106</t>
+          <t>1131046</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034106</t>
+          <t>1131046</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034106</t>
+          <t>1131046</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4651,17 +4651,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>976780</t>
+          <t>859892</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>976780</t>
+          <t>859892</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>976780</t>
+          <t>859892</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4686,17 +4686,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2010887</t>
+          <t>1990938</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2010887</t>
+          <t>1990938</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2010887</t>
+          <t>1990938</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4733,32 +4733,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>74983</t>
+          <t>81107</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>59570</t>
+          <t>63873</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>92659</t>
+          <t>99748</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4768,32 +4768,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>137320</t>
+          <t>151956</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>106957</t>
+          <t>134404</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>163025</t>
+          <t>169273</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4803,32 +4803,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>212304</t>
+          <t>233063</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>173888</t>
+          <t>208602</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>238850</t>
+          <t>258538</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,48%</t>
         </is>
       </c>
     </row>
@@ -4846,32 +4846,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>400063</t>
+          <t>486857</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>382387</t>
+          <t>468216</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>415476</t>
+          <t>504091</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4881,32 +4881,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>704015</t>
+          <t>678894</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>678310</t>
+          <t>661577</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>734378</t>
+          <t>696446</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4916,32 +4916,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1104077</t>
+          <t>1165751</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1077531</t>
+          <t>1140276</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1142493</t>
+          <t>1190212</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>81,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>85,09%</t>
         </is>
       </c>
     </row>
@@ -4959,17 +4959,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4994,17 +4994,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5029,17 +5029,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5061,7 +5061,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5076,32 +5076,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10913</t>
+          <t>10117</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4683</t>
+          <t>4521</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23348</t>
+          <t>20201</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5111,32 +5111,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>105303</t>
+          <t>115432</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>89735</t>
+          <t>98281</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>123979</t>
+          <t>136557</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5146,32 +5146,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>116216</t>
+          <t>125549</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>98650</t>
+          <t>107925</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>136489</t>
+          <t>149304</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,81%</t>
         </is>
       </c>
     </row>
@@ -5189,32 +5189,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>229594</t>
+          <t>227111</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>217159</t>
+          <t>217027</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>235824</t>
+          <t>232707</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5224,32 +5224,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>655389</t>
+          <t>728164</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>636713</t>
+          <t>707039</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>670957</t>
+          <t>745315</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5259,32 +5259,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>884984</t>
+          <t>955275</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>864711</t>
+          <t>931520</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>902550</t>
+          <t>972899</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,01%</t>
         </is>
       </c>
     </row>
@@ -5302,17 +5302,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5337,17 +5337,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>760692</t>
+          <t>843596</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>760692</t>
+          <t>843596</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>760692</t>
+          <t>843596</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5372,17 +5372,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001200</t>
+          <t>1080824</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001200</t>
+          <t>1080824</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001200</t>
+          <t>1080824</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5419,32 +5419,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>743956</t>
+          <t>521537</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>522012</t>
+          <t>476731</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1237063</t>
+          <t>563912</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5454,32 +5454,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>619202</t>
+          <t>685787</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>509976</t>
+          <t>647537</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>679388</t>
+          <t>727178</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5489,22 +5489,22 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1363157</t>
+          <t>1207324</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1126807</t>
+          <t>1146992</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2025922</t>
+          <t>1270614</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>17,96%</t>
         </is>
       </c>
     </row>
@@ -5532,32 +5532,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2630645</t>
+          <t>2919268</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2137538</t>
+          <t>2876893</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2852589</t>
+          <t>2964074</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5567,32 +5567,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2955355</t>
+          <t>2946286</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2895169</t>
+          <t>2904895</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3064581</t>
+          <t>2984536</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5602,27 +5602,27 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>5586001</t>
+          <t>5865554</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4923236</t>
+          <t>5802264</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5822351</t>
+          <t>5925886</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>82,93%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -5645,17 +5645,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3374601</t>
+          <t>3440805</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3374601</t>
+          <t>3440805</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3374601</t>
+          <t>3440805</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5680,17 +5680,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3574557</t>
+          <t>3632073</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3574557</t>
+          <t>3632073</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3574557</t>
+          <t>3632073</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -5715,17 +5715,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6949158</t>
+          <t>7072878</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6949158</t>
+          <t>7072878</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6949158</t>
+          <t>7072878</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
